--- a/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-23T12:05:04+00:00</t>
+    <t>2022-08-23T16:03:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-23T16:03:23+00:00</t>
+    <t>2022-08-23T16:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-23T16:03:37+00:00</t>
+    <t>2022-08-24T08:06:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
+++ b/branches/jose/StructureDefinition-InvestigationalMedicinalProduct.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-24T08:06:58+00:00</t>
+    <t>2022-08-24T08:07:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
